--- a/AAII_Financials/Yearly/AHI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AHI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -857,7 +857,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="E14" s="3">
         <v>1700</v>
@@ -921,10 +921,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15500</v>
+        <v>15800</v>
       </c>
       <c r="E17" s="3">
-        <v>10200</v>
+        <v>10300</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>3</v>
@@ -948,10 +948,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-15100</v>
+        <v>-15400</v>
       </c>
       <c r="E18" s="3">
-        <v>-9300</v>
+        <v>-9500</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -1015,10 +1015,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-15200</v>
+        <v>-15500</v>
       </c>
       <c r="E21" s="3">
-        <v>-9600</v>
+        <v>-9700</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1069,10 +1069,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-15200</v>
+        <v>-15500</v>
       </c>
       <c r="E23" s="3">
-        <v>-9600</v>
+        <v>-9800</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -1150,10 +1150,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-14600</v>
+        <v>-14900</v>
       </c>
       <c r="E26" s="3">
-        <v>-9100</v>
+        <v>-9300</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -1177,10 +1177,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-14600</v>
+        <v>-14900</v>
       </c>
       <c r="E27" s="3">
-        <v>-9100</v>
+        <v>-9300</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -1339,10 +1339,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-14600</v>
+        <v>-14900</v>
       </c>
       <c r="E33" s="3">
-        <v>-9100</v>
+        <v>-9300</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -1393,10 +1393,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-14600</v>
+        <v>-14900</v>
       </c>
       <c r="E35" s="3">
-        <v>-9100</v>
+        <v>-9300</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>3</v>
@@ -1478,7 +1478,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>3</v>
@@ -1613,7 +1613,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>3</v>
@@ -1829,7 +1829,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>3</v>
@@ -2273,7 +2273,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-34500</v>
+        <v>-35000</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>3</v>
@@ -2381,7 +2381,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>3</v>
@@ -2467,10 +2467,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-14600</v>
+        <v>-14900</v>
       </c>
       <c r="E81" s="3">
-        <v>-9100</v>
+        <v>-9300</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>3</v>
@@ -2669,7 +2669,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-6400</v>
+        <v>-6500</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>3</v>
@@ -2938,7 +2938,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
